--- a/nifty_option_data_cache.xlsx
+++ b/nifty_option_data_cache.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_2A2A2FC623F75D7B1953BE50881CA817A89381B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="3015" windowWidth="15375" windowHeight="7785" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="1" r:id="rId1"/>
@@ -238,14 +238,14 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,128 +466,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="23.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
     </row>
     <row r="5" spans="1:8" ht="15">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
     </row>
     <row r="6" spans="1:8" ht="15">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
     </row>
     <row r="7" spans="1:8" ht="15">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
     </row>
     <row r="8" spans="1:8" ht="15">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
     </row>
     <row r="9" spans="1:8" ht="15">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
     </row>
     <row r="10" spans="1:8" ht="15">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2"/>
@@ -600,65 +600,70 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A15:H15"/>
@@ -668,11 +673,6 @@
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
